--- a/AAII_Financials/Quarterly/AMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>AMT</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2737500</v>
+        <v>2749100</v>
       </c>
       <c r="E8" s="3">
         <v>2737500</v>
       </c>
       <c r="F8" s="3">
+        <v>2737500</v>
+      </c>
+      <c r="G8" s="3">
         <v>2717400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2626900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2562800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2547600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2522300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2544700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2512600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>2521100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2767200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2705000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2671500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2674300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2660300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2445200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2454300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2298900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2158500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2122500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2012900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1913000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1993100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1923700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1953600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1889600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1813400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2131900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1785500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1780900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1741800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1704500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1680800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1662400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1616200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1539500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1514800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>741300</v>
+      </c>
+      <c r="E9" s="3">
         <v>703300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>714100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>710800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>688700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>634500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>654400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>651800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>649300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>618900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>638000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>806100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>805000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>836500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>822900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>799400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>735500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>724300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>647900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>574300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>572600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>562600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>540000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>552000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>550200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>559900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>563300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>543400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>540900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>556700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>560300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>519900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>527000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>519800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>517200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>492700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>488000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>491200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2007800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2034200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2023400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2006600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1938200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1928300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1893200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1870500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1895400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1893700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>1883100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1961100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1900000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1835000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1851400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1860900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1709700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1730000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1651000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1584200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1549900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1450300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1373000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1441100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1373500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1393700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1326300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1270000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1591000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1228800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1220600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1221900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1177600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1161000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1145200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1123500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1051500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1023600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,252 +1497,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>77500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-8400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-109100</v>
-      </c>
       <c r="H14" s="3">
+        <v>-110700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-61200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>76700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-64000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-36800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>108600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>674300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>278700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>32200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>37900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>72900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>209900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>49600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>32100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>38300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>162500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>106200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>35100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>145300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>183200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>14200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>55400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>514400</v>
+      </c>
+      <c r="E15" s="3">
         <v>518200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>515900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>522900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>510300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>492500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>498500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>520600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>508800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>606900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>723200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>764600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>794100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>814700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>898100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>826500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>815800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>643900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>611400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>554800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>522500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>481200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>473900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>454900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>472300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>449800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>442800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>448900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>436900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>765900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>448900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>449700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>446300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>466100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>432400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>396400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>421100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>388200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>398000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1480800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1507200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1481600</v>
       </c>
-      <c r="G17" s="3">
-        <v>1427600</v>
-      </c>
       <c r="H17" s="3">
+        <v>1429200</v>
+      </c>
+      <c r="I17" s="3">
         <v>1362300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1414300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1379200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1384600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1371600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>1598300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1881800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2513000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2019000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1892000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1935200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1831100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1626800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1449700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1355500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1448200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1265000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1221700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1290900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1262400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1225300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1227800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1198600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1746300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1218300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1234900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1338900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1375800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1133800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1085800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1140300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1049900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1035800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1248400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1256700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1230300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1235800</v>
       </c>
-      <c r="G18" s="3">
-        <v>1199300</v>
-      </c>
       <c r="H18" s="3">
+        <v>1197700</v>
+      </c>
+      <c r="I18" s="3">
         <v>1200500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1133300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1143100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1160100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1141000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>922800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>885400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>192000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>652500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>782300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>725100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>614100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>827500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>849200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>803000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>674300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>747900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>691300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>702200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>661300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>728300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>661800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>614800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>385600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>567200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>546000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>402900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>328700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>547000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>576600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>475900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>489600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>479000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,618 +2086,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-65800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-116100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>484600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>345800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-538200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>337500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-127800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>-238700</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>99000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-647100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>497300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>392600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>262500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>138500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>176200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>185200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>106600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-58500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-54800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-34100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-53700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>8500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>15000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>34300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>20500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>32700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>46200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>10200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>23200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>42300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-9500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1804600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1840700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1862300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1775500</v>
       </c>
-      <c r="G21" s="3">
-        <v>1225000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1223400</v>
+      </c>
+      <c r="I21" s="3">
         <v>1347200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2172400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1304100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1659400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1777600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>606900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1884700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>764600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1580500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>359600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2047900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2001400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1803400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1396500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1615100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1589200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1432100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1097000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1112100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1120800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1119600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1186100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1117300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1086000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1172000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1048800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>975900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>895400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>797900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>989500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>996200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>939300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>868300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>874200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>354500</v>
+      </c>
+      <c r="E22" s="3">
         <v>347300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>344400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>347100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>342600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>325300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>321200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>356800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>362700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>363800</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>356500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>340200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>303500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>294000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>276600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>262400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>224100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>226100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>213700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>207000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>196100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>190900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>197700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>208800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>200900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>201300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>204500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>207500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>208800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>210100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>207900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>199900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>190400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>189100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>187300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>184000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>186400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>190400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1009300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1018100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>964900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>950000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>511800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>617500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1305700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>550500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>847300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>921300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>824300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>368400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-758600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>855800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>898300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>725200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>528500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>777600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>820700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>702600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>419700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>502200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>459500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>439700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>468900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>542000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>463900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>441600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>197300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>389800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>318300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>249200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>141400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>368100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>412500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>334200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>293700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>285800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E24" s="3">
         <v>139600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>128100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>131300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>118900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>122400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>91300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>49500</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>53400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-42000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>36100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>87300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>51400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>72800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>50300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>58100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>36700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>29600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-95400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>12500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-31100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-35700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>33400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>24000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>26800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>60800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>887500</v>
+      </c>
+      <c r="E26" s="3">
         <v>878500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>836800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>912600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>380500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>498600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1230500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>428100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>769900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>830000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>774800</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>315000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-716600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>819700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>890900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>702700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>441200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>726200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>747900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>652300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>361600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>462900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>448400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>418600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>569400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>505300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>434300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>407600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>292700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>377300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>314400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>280300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>177000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>334700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>388500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>307400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>232900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>263700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>867500</v>
+      </c>
+      <c r="E27" s="3">
         <v>859500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>820700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>853300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>366800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>488700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1229600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-792300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>900300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>917400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>586900</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>335800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-683800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>839700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>898200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>711700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>453400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>723000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>746300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>645000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>365100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>464400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>446100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>415000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>562700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>498600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>429100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>397400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>277600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>366900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>306700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>275800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>201800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>298400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>344200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>289300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>202400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>237700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3175,23 +3236,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1208500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>138500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>91700</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-197500</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -3256,11 +3317,11 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>17800</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E32" s="3">
         <v>65800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>116100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-484600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-345800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>538200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-337500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>127800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>238700</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>647100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-497300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-392600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-262500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-138500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-176200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-185200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-106600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>58500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>54800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>34100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>53700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-34300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-32700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-46200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-10200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-23200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-42300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>9500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>867500</v>
+      </c>
+      <c r="E33" s="3">
         <v>859500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>820700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>853300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>366800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>488700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1229600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-792300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>900300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>917400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>586900</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>335800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-683800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>839700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>898200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>711700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>453400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>723000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>746300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>645000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>365100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>464400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>446100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>415000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>562700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>498600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>429100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>397400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>277600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>366900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>306700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>275800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>219600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>298400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>344200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>289300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>202400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>237700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>867500</v>
+      </c>
+      <c r="E35" s="3">
         <v>859500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>820700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>853300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>366800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>488700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1229600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-792300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>900300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>917400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>586900</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>335800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-683800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>839700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>898200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>711700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>453400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>723000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>746300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>645000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>365100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>464400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>446100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>415000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>562700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>498600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>429100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>397400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>277600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>366900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>306700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>275800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>219600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>298400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>344200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>289300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>202400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>237700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1762500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1608800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1474800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1950700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2076000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2103700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1999600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2150300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2492100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2389100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1753700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2118900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2015700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1803000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2028400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2121800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2066700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1941500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1949900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3277200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1928000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1913600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1746300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1626000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2038100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1326000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1501200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1352600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1192200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1004800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1208700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1026500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>834500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1125400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>802100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>799500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>770000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>712800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>787200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>530400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4428,26 +4518,26 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG42" s="3">
         <v>18400</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
       <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
         <v>68200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>80800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>389400</v>
-      </c>
-      <c r="AK42" s="3">
-        <v>1000</v>
       </c>
       <c r="AL42" s="3">
         <v>1000</v>
@@ -4456,138 +4546,144 @@
         <v>1000</v>
       </c>
       <c r="AN42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AO42" s="3">
         <v>5300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>4000</v>
       </c>
-      <c r="AP42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>889600</v>
+      </c>
+      <c r="E43" s="3">
         <v>957800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>889600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1057400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>968300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>784800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>812700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1116900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1180200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>813200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1047800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1071400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1072100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1125700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1119000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1169600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1187100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1082400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1079500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1017100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>756600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>754800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>744200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>732300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>754600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>675800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>630700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>656900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>689400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>671400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>744100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>724700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>732200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>822200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>768200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>607700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>610300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>524700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>468300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4630,8 +4726,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4708,618 +4804,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E45" s="3">
         <v>260700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>247000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>434600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>334400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>298600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>285800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>304700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>378600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>350900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1023400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>570500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>460600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>452600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>468200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>518200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>489300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>663300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>697100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>685200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>410900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>351400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>404500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>482300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>456200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>424300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>376800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>378700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>383300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>349700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>505000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>598200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>487100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>550400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>412800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>394900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>424000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>382800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>373900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>372100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3122400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2956400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2741800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3535400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3601400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3506100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3178800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3399600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4114100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4047800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3710000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3849900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3681400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3450100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3622300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3759000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3725600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3791900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3729400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5041900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3356000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3021600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2905600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2852500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3226600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2504900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2553800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2362000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2232400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2062300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2385100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2437000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2127100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2797400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2038100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1963600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1802800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1711200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1689900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1370800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>213300</v>
+      </c>
+      <c r="E47" s="3">
         <v>201300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>176900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>233100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>222200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>111500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>103900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>127400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>59500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>210700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>24400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>546700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>492800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>427400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>423800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>400900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>395400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>401800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>394100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>400100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>315200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>393400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>407000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>406400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>248900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>263800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>279100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>962600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>978300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1024500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>990300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>950100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>931500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>888900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>863400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>841500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29039200</v>
+      </c>
+      <c r="E48" s="3">
         <v>28933300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28782800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28555200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28183500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>27432600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>27146400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>27606400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28939800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29294000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27068300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28413100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28740500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28795700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28917200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28260100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28875200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29183500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29009100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23290000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23409700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20432400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20597900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18895600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18479800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18419600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19441800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18497900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18378600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18283500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11247100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10996300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11067000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>11294800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>11101000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>10795100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>10725700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>10717200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10517300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>10452000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26162100</v>
+      </c>
+      <c r="E49" s="3">
         <v>26417800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26786200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26997900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27208600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26564000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26242400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27240800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28242200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28676100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28015800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29224800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30336700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30634300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>30940000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31006500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>32195100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>33531400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>34077300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>29249200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>29360400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>20769700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>21122500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>17365900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>17436200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>17549400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>18496700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>16377200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>16453000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>16581000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>16676200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>16945100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>17284800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>17587300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>17421700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>16952700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>17099800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>17206700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16345300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>16555200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4588000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4572200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4551300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4401100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4381800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4308400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4283200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4299300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4343000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4289200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7020900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4014000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3966100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3799800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3168300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2994400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2893500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2832900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2671200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2553500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2455000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2324700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2207400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2033000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1979900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1908200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1902900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1821200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1744900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1720900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1739400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1720500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1702300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1702900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1703400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1676500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1621100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1559000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1485200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1463600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63300100</v>
+      </c>
+      <c r="E54" s="3">
         <v>63234600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63190400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>63888700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>63754500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62055600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>61077400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62816800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65837800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66679000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66027600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>65653000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>66879000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66817700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67194500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66512800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>68116800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>69763500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>69887900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60530000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58982900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46942500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>47233500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>41462200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>41515900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>40789100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42801600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39307200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>39072700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38926800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>33010400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33077200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>33205700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>34372700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>33214300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>32319300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>32138200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>32057400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>30879200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>30655500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,740 +6146,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>202800</v>
+      </c>
+      <c r="E57" s="3">
         <v>220800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>259800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>239000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>229700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>199600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>240800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>221300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>206000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>182100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>251300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>216200</v>
       </c>
       <c r="O57" s="3">
         <v>216200</v>
       </c>
       <c r="P57" s="3">
+        <v>216200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>206000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>218600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>212000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>194500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>215400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>367600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>231500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>212000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>145800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>198000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>117000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>108200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>120600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>148100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>136200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>144900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>130000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>130800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>122900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>137000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>118700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>142900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>119700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>102700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>109400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>118700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>105600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5870600</v>
+      </c>
+      <c r="E58" s="3">
         <v>6760900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3972700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3003100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2904400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3409400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4269700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4330300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4032600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3782800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3757700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3937100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3999600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4646500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4514200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3015200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3603900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5309900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4568700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2106400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2636000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1336500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>789800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>771300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3366000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2640000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2928200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2443600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2442200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2097200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2754800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2841300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2791800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2803200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>774800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>687400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1732000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1707300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>238800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1847900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1784900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1630200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1761800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1695900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1702800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1534700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1580500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1534800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1678100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2163800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1608000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1628200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1676500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3579100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3395400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3663300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3774700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4131000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4186200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3104100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2714300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2667700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2377800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2470700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2393800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2411400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2207600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2234500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2184700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1804300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1615500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1634100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1622800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1594400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1453100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1444200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1392300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1273800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1171000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8870500</v>
+      </c>
+      <c r="E60" s="3">
         <v>9719400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6913800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5993500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5863600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6322000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7075600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7069500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6888700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6729800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7249300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6868700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6925700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7532100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8311900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6622600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7461700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9300000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9067300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6524100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5952100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4196600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3655500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3266100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5944900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5154400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5487700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4787400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4821600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4411900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4689900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4579700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4562900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4544700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2512100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2260200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3278900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3209100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1631300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1519600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39109300</v>
+      </c>
+      <c r="E61" s="3">
         <v>38370300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>40991200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>42008100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42308800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40974200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39684400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40451000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>43356900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44058200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42549300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42879100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43176900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42262500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>34156000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35313900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>37240100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38154500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38685500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31439000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32947600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27990300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28497700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>24011000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>21849200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21937400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21127200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>19040000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18615900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19107100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>18405100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18422900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>18322000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18568800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>19430300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18581400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>17509900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>17182800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>18294700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>18436100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3494200</v>
+      </c>
+      <c r="E62" s="3">
         <v>3495400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3489800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3607800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3557200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3465200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3406700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3702000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3769400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3834900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3578100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3248100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3281500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3267200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12318100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12257700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12688800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13058300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13065500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12878500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13050400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10203800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10299800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9441100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9119200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9091300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9599800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9109900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9001900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8918500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3011000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3191100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3184900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3252700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3317600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3221300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3148400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3150700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2885800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2825300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53047600</v>
+      </c>
+      <c r="E66" s="3">
         <v>53082500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52835100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53122800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53275600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52119300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51428700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52623900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55414300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>56017300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55162200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54418500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>54871800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54567400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>61622100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60231000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>61158100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64400500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64806700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55118800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>53228700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43059100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43140000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>37730500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>37895600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37154700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>37746200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>34066800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33595200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33579800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>27674300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>27726500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>27655000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>28038500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>26972800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>25801200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>25655500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>25204900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>24115300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>23948100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7638,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="AN70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AO70" s="3">
         <v>100</v>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>100</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,8 +7939,11 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7812,86 +7986,89 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>-2101900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-689300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-842300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1072400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1142400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-960400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1085000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1251800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1343000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1168800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1125100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1082500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1016800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1130100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1206200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1226400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1199500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1104300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1121600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-1085700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-1058100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-975200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-989200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-1053700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-1030700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3719700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3522600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3652500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3952700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3712800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3534800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3382200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3641700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3856000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4047800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4198200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4533300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5166400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5406600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5572400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6281800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6958700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5363000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5081200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5411200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5754200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3883400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4093500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3731700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3620300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3634400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5055400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5240400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5477500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5347000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5336100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5350700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5550700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6334200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6241500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6518100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6482700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6852400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6763800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6707300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>867500</v>
+      </c>
+      <c r="E81" s="3">
         <v>859500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>820700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>853300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>366800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>488700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1229600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-792300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>900300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>917400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>586900</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>335800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-683800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>839700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>898200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>711700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>453400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>723000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>746300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>645000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>365100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>464400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>446100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>415000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>562700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>498600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>429100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>397400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>277600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>366900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>306700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>275800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>219600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>298400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>344200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>289300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>202400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>237700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E83" s="3">
         <v>278400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>152400</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>378100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>279400</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>490600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>424600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>299900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>517600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>365600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>357200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>814700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>898100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>826500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>815800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>643900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>611400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>554800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>522500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>481200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>473900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>454900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>472300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>449800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>442800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>448900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>436900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>765900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>448900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>449700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>446300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>466100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>432300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>396400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>421100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>388200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>398000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1486800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1400600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1427500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1460000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1281500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1295000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1199000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>1338500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1283600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>1300600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1070500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1185000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>932300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>915300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>663600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>678900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2096400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>951900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1092700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1132300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>960300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>988800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>800000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>993700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>937200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1036600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>785100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1263200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>753300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>940000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>791800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>789000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>658100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>795400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>683100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>725200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>667100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,31 +9911,32 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-320900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-449500</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-579200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-465500</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-304600</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-331100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-443400</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
@@ -9735,86 +9956,89 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-658200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-459200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-370100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-386100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-460000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-314000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-277900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-324800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-362900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-243900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-210500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-214400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-266700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-260300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-243500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-220800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-302800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-185500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-226400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-198500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-248600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-183500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-203400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-336200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-889800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-155700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-360000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-473700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-468100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-550500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-491100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-350100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-360700</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-89200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-436100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-449100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-276800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-849000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-602700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-390400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-513100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10167700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1018900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9066900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-438700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3814000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-331800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-385400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-253400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2586700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-810100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-267400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-323300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-694400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-212100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-562400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1280600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1290400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-296000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-294200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-920300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-316100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-242800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>834700</v>
+      </c>
+      <c r="E96" s="3">
         <v>806600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>796200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>796300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>796200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>768500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>758000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>757100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>802100</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>731900</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>733600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-684500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-665800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-638900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-641200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-596600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-578000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-551500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-544900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-506400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-488000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-478900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-454900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-420800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-407100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-398000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-377100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-348400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-339500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-331300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-304300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-283500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-274600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-264500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-250400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-234100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-225400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-971700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-831000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1443800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1014200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-906700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-843800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-908500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1027900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-390200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-707700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1012600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-462700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-205100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-504500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-250900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8141700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>695800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8067000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-480000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2734700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1012600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>99200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-606000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1696300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>72800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-597000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-650400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-573400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-222700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-628900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>817300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>500900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-323300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-448500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>157900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-303500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E101" s="3">
         <v>29900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-103800</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>-119500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-34000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-61600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
         <v>3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>17800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-78000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-88700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>28500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>17800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-78000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-88700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>28500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-74800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>55500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-42100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>78200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-118300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>26400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>14100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-57500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>6000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-17200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E102" s="3">
         <v>132700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-495600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-108800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>131000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-174000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>101900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>423300</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>82200</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-215300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-108900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>46500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-68300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-71900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1356000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1698500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>131900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>131200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-375900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>705800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-177700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>129700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>162300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>186300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-205200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>323200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-308800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>324000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>35300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>57200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-74400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>263900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>119800</v>
       </c>
     </row>
